--- a/artfynd/A 47429-2023 artfynd.xlsx
+++ b/artfynd/A 47429-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122917623</v>
       </c>
       <c r="B2" t="n">
-        <v>56529</v>
+        <v>56532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47429-2023 artfynd.xlsx
+++ b/artfynd/A 47429-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122917623</v>
       </c>
       <c r="B2" t="n">
-        <v>56532</v>
+        <v>56538</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
